--- a/evaluations/test_reports/throughput/Elapsed_Time/1_Client/direct_client/extracted_stats.xlsx
+++ b/evaluations/test_reports/throughput/Elapsed_Time/1_Client/direct_client/extracted_stats.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D50"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,511 +452,511 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1681822685</v>
+        <v>1681822696</v>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>97.875</v>
+        <v>97.2</v>
       </c>
       <c r="D2" t="n">
-        <v>9.873565344552144</v>
+        <v>10.17305127900351</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1681822686</v>
+        <v>1681822697</v>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>98.11111099999999</v>
+        <v>95.7</v>
       </c>
       <c r="D3" t="n">
-        <v>9.906571355303898</v>
+        <v>10.18659370565303</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1681822687</v>
+        <v>1681822698</v>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>98.7</v>
+        <v>94.7</v>
       </c>
       <c r="D4" t="n">
-        <v>9.881723582698427</v>
+        <v>10.1388561109383</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1681822688</v>
+        <v>1681822699</v>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>100.4</v>
+        <v>93.8</v>
       </c>
       <c r="D5" t="n">
-        <v>9.979178544142004</v>
+        <v>10.184267475102</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1681822689</v>
+        <v>1681822700</v>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>99</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="D6" t="n">
-        <v>9.988913926710207</v>
+        <v>10.15730638523611</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1681822690</v>
+        <v>1681822701</v>
       </c>
       <c r="B7" t="n">
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>100.8</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="D7" t="n">
-        <v>10.02937073467796</v>
+        <v>10.14235472472471</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1681822691</v>
+        <v>1681822702</v>
       </c>
       <c r="B8" t="n">
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>99.40000000000001</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="D8" t="n">
-        <v>10.06574762397024</v>
+        <v>10.10776206090455</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1681822692</v>
+        <v>1681822703</v>
       </c>
       <c r="B9" t="n">
         <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>98</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="D9" t="n">
-        <v>10.13442615395812</v>
+        <v>10.17697713448613</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1681822694</v>
+        <v>1681822704</v>
       </c>
       <c r="B10" t="n">
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>98.90000000000001</v>
+        <v>97.5</v>
       </c>
       <c r="D10" t="n">
-        <v>10.11279700645085</v>
+        <v>10.17976981957134</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1681822695</v>
+        <v>1681822705</v>
       </c>
       <c r="B11" t="n">
         <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>96.90000000000001</v>
+        <v>97</v>
       </c>
       <c r="D11" t="n">
-        <v>10.16326477717618</v>
+        <v>10.17576564293522</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1681822696</v>
+        <v>1681822706</v>
       </c>
       <c r="B12" t="n">
         <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>97.2</v>
+        <v>96.3</v>
       </c>
       <c r="D12" t="n">
-        <v>10.17305127900351</v>
+        <v>10.144073444727</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1681822697</v>
+        <v>1681822707</v>
       </c>
       <c r="B13" t="n">
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>95.7</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="D13" t="n">
-        <v>10.18659370565303</v>
+        <v>10.13276400163655</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1681822698</v>
+        <v>1681822708</v>
       </c>
       <c r="B14" t="n">
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>94.7</v>
+        <v>98.3</v>
       </c>
       <c r="D14" t="n">
-        <v>10.1388561109383</v>
+        <v>10.06709993142664</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1681822699</v>
+        <v>1681822709</v>
       </c>
       <c r="B15" t="n">
         <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>93.8</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="D15" t="n">
-        <v>10.184267475102</v>
+        <v>10.09304756315402</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1681822700</v>
+        <v>1681822710</v>
       </c>
       <c r="B16" t="n">
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>94.59999999999999</v>
+        <v>100.3</v>
       </c>
       <c r="D16" t="n">
-        <v>10.15730638523611</v>
+        <v>10.13078289889844</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1681822701</v>
+        <v>1681822711</v>
       </c>
       <c r="B17" t="n">
         <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>94.90000000000001</v>
+        <v>100.1</v>
       </c>
       <c r="D17" t="n">
-        <v>10.14235472472471</v>
+        <v>10.15992493184118</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1681822702</v>
+        <v>1681822712</v>
       </c>
       <c r="B18" t="n">
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>95.40000000000001</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="D18" t="n">
-        <v>10.10776206090455</v>
+        <v>10.17970604607954</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1681822703</v>
+        <v>1681822713</v>
       </c>
       <c r="B19" t="n">
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>96.09999999999999</v>
+        <v>97.7</v>
       </c>
       <c r="D19" t="n">
-        <v>10.17697713448613</v>
+        <v>10.20123841057361</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1681822704</v>
+        <v>1681822714</v>
       </c>
       <c r="B20" t="n">
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>97.5</v>
+        <v>95.7</v>
       </c>
       <c r="D20" t="n">
-        <v>10.17976981957134</v>
+        <v>10.17282592622857</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1681822705</v>
+        <v>1681822715</v>
       </c>
       <c r="B21" t="n">
         <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>97</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="D21" t="n">
-        <v>10.17576564293522</v>
+        <v>10.17766554497596</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1681822706</v>
+        <v>1681822716</v>
       </c>
       <c r="B22" t="n">
         <v>1</v>
       </c>
       <c r="C22" t="n">
-        <v>96.3</v>
+        <v>97.5</v>
       </c>
       <c r="D22" t="n">
-        <v>10.144073444727</v>
+        <v>10.1832954507125</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1681822707</v>
+        <v>1681822717</v>
       </c>
       <c r="B23" t="n">
         <v>1</v>
       </c>
       <c r="C23" t="n">
-        <v>96.59999999999999</v>
+        <v>98</v>
       </c>
       <c r="D23" t="n">
-        <v>10.13276400163655</v>
+        <v>10.15116935823022</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1681822708</v>
+        <v>1681822718</v>
       </c>
       <c r="B24" t="n">
         <v>1</v>
       </c>
       <c r="C24" t="n">
-        <v>98.3</v>
+        <v>96.2</v>
       </c>
       <c r="D24" t="n">
-        <v>10.06709993142664</v>
+        <v>10.18722000915469</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1681822709</v>
+        <v>1681822719</v>
       </c>
       <c r="B25" t="n">
         <v>1</v>
       </c>
       <c r="C25" t="n">
-        <v>99.40000000000001</v>
+        <v>97.2</v>
       </c>
       <c r="D25" t="n">
-        <v>10.09304756315402</v>
+        <v>10.16622716467632</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1681822710</v>
+        <v>1681822720</v>
       </c>
       <c r="B26" t="n">
         <v>1</v>
       </c>
       <c r="C26" t="n">
-        <v>100.3</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="D26" t="n">
-        <v>10.13078289889844</v>
+        <v>10.13190891394065</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1681822711</v>
+        <v>1681822721</v>
       </c>
       <c r="B27" t="n">
         <v>1</v>
       </c>
       <c r="C27" t="n">
-        <v>100.1</v>
+        <v>95.2</v>
       </c>
       <c r="D27" t="n">
-        <v>10.15992493184118</v>
+        <v>10.12685619704889</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>1681822712</v>
+        <v>1681822722</v>
       </c>
       <c r="B28" t="n">
         <v>1</v>
       </c>
       <c r="C28" t="n">
-        <v>98.90000000000001</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="D28" t="n">
-        <v>10.17970604607954</v>
+        <v>10.11872757226229</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>1681822713</v>
+        <v>1681822723</v>
       </c>
       <c r="B29" t="n">
         <v>1</v>
       </c>
       <c r="C29" t="n">
-        <v>97.7</v>
+        <v>98.8</v>
       </c>
       <c r="D29" t="n">
-        <v>10.20123841057361</v>
+        <v>10.12583613370343</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>1681822714</v>
+        <v>1681822724</v>
       </c>
       <c r="B30" t="n">
         <v>1</v>
       </c>
       <c r="C30" t="n">
-        <v>95.7</v>
+        <v>100.3</v>
       </c>
       <c r="D30" t="n">
-        <v>10.17282592622857</v>
+        <v>10.12365430339088</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>1681822715</v>
+        <v>1681822725</v>
       </c>
       <c r="B31" t="n">
         <v>1</v>
       </c>
       <c r="C31" t="n">
-        <v>96.59999999999999</v>
+        <v>100.3</v>
       </c>
       <c r="D31" t="n">
-        <v>10.17766554497596</v>
+        <v>10.12439895094487</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>1681822716</v>
+        <v>1681822726</v>
       </c>
       <c r="B32" t="n">
         <v>1</v>
       </c>
       <c r="C32" t="n">
-        <v>97.5</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="D32" t="n">
-        <v>10.1832954507125</v>
+        <v>10.12887912733453</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>1681822717</v>
+        <v>1681822727</v>
       </c>
       <c r="B33" t="n">
         <v>1</v>
       </c>
       <c r="C33" t="n">
-        <v>98</v>
+        <v>100.1</v>
       </c>
       <c r="D33" t="n">
-        <v>10.15116935823022</v>
+        <v>10.13456026650636</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>1681822718</v>
+        <v>1681822728</v>
       </c>
       <c r="B34" t="n">
         <v>1</v>
       </c>
       <c r="C34" t="n">
-        <v>96.2</v>
+        <v>100.2</v>
       </c>
       <c r="D34" t="n">
-        <v>10.18722000915469</v>
+        <v>10.13962677468129</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>1681822719</v>
+        <v>1681822729</v>
       </c>
       <c r="B35" t="n">
         <v>1</v>
       </c>
       <c r="C35" t="n">
-        <v>97.2</v>
+        <v>98.3</v>
       </c>
       <c r="D35" t="n">
-        <v>10.16622716467632</v>
+        <v>10.16808835978935</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>1681822720</v>
+        <v>1681822730</v>
       </c>
       <c r="B36" t="n">
         <v>1</v>
       </c>
       <c r="C36" t="n">
-        <v>93.40000000000001</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="D36" t="n">
-        <v>10.13190891394065</v>
+        <v>10.14531971950768</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>1681822721</v>
+        <v>1681822731</v>
       </c>
       <c r="B37" t="n">
         <v>1</v>
       </c>
       <c r="C37" t="n">
-        <v>95.2</v>
+        <v>98</v>
       </c>
       <c r="D37" t="n">
-        <v>10.12685619704889</v>
+        <v>10.20414958791411</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>1681822722</v>
+        <v>1681822732</v>
       </c>
       <c r="B38" t="n">
         <v>1</v>
@@ -965,174 +965,34 @@
         <v>97.40000000000001</v>
       </c>
       <c r="D38" t="n">
-        <v>10.11872757226229</v>
+        <v>10.296220063166</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>1681822723</v>
+        <v>1681822733</v>
       </c>
       <c r="B39" t="n">
         <v>1</v>
       </c>
       <c r="C39" t="n">
-        <v>98.8</v>
+        <v>93.3</v>
       </c>
       <c r="D39" t="n">
-        <v>10.12583613370343</v>
+        <v>10.38367559435392</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>1681822724</v>
+        <v>1681822734</v>
       </c>
       <c r="B40" t="n">
         <v>1</v>
       </c>
       <c r="C40" t="n">
-        <v>100.3</v>
+        <v>88.8</v>
       </c>
       <c r="D40" t="n">
-        <v>10.12365430339088</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>1681822725</v>
-      </c>
-      <c r="B41" t="n">
-        <v>1</v>
-      </c>
-      <c r="C41" t="n">
-        <v>100.3</v>
-      </c>
-      <c r="D41" t="n">
-        <v>10.12439895094487</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>1681822726</v>
-      </c>
-      <c r="B42" t="n">
-        <v>1</v>
-      </c>
-      <c r="C42" t="n">
-        <v>99.90000000000001</v>
-      </c>
-      <c r="D42" t="n">
-        <v>10.12887912733453</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>1681822727</v>
-      </c>
-      <c r="B43" t="n">
-        <v>1</v>
-      </c>
-      <c r="C43" t="n">
-        <v>100.1</v>
-      </c>
-      <c r="D43" t="n">
-        <v>10.13456026650636</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>1681822728</v>
-      </c>
-      <c r="B44" t="n">
-        <v>1</v>
-      </c>
-      <c r="C44" t="n">
-        <v>100.2</v>
-      </c>
-      <c r="D44" t="n">
-        <v>10.13962677468129</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>1681822729</v>
-      </c>
-      <c r="B45" t="n">
-        <v>1</v>
-      </c>
-      <c r="C45" t="n">
-        <v>98.3</v>
-      </c>
-      <c r="D45" t="n">
-        <v>10.16808835978935</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>1681822730</v>
-      </c>
-      <c r="B46" t="n">
-        <v>1</v>
-      </c>
-      <c r="C46" t="n">
-        <v>99.90000000000001</v>
-      </c>
-      <c r="D46" t="n">
-        <v>10.14531971950768</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>1681822731</v>
-      </c>
-      <c r="B47" t="n">
-        <v>1</v>
-      </c>
-      <c r="C47" t="n">
-        <v>98</v>
-      </c>
-      <c r="D47" t="n">
-        <v>10.20414958791411</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>1681822732</v>
-      </c>
-      <c r="B48" t="n">
-        <v>1</v>
-      </c>
-      <c r="C48" t="n">
-        <v>97.40000000000001</v>
-      </c>
-      <c r="D48" t="n">
-        <v>10.296220063166</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>1681822733</v>
-      </c>
-      <c r="B49" t="n">
-        <v>1</v>
-      </c>
-      <c r="C49" t="n">
-        <v>93.3</v>
-      </c>
-      <c r="D49" t="n">
-        <v>10.38367559435392</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>1681822734</v>
-      </c>
-      <c r="B50" t="n">
-        <v>1</v>
-      </c>
-      <c r="C50" t="n">
-        <v>88.8</v>
-      </c>
-      <c r="D50" t="n">
         <v>10.44817361034244</v>
       </c>
     </row>
